--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 08/XKSX_VoHopTG102LE(UPG)_170826.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 08/XKSX_VoHopTG102LE(UPG)_170826.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Xuất kho\Tháng 08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D4CD9C-7123-49F2-A41C-C56C2E11AA47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD18533-428B-4C7A-8E4E-2B69FF4A42BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="XuatKho_SX" sheetId="10" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">XuatKho_SX!$A$1:$M$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">XuatKho_SX!$A$1:$M$19</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>STT</t>
   </si>
@@ -99,13 +99,19 @@
     <t>Họ và tên người đề nghị: Nguyễn Minh Tùng</t>
   </si>
   <si>
-    <t>Hà Nội, ngày 17 tháng 08 năm 2026</t>
-  </si>
-  <si>
     <t>Phòngban/ Bộ phận: PKT/ Bảo hành - Sản xuất</t>
   </si>
   <si>
     <t>Chiếc</t>
+  </si>
+  <si>
+    <t>Sản xuất thành phẩm TG102LE nâng cấp 2G =&gt; 4G</t>
+  </si>
+  <si>
+    <t>VT_Vỏ hộp_TG102LE</t>
+  </si>
+  <si>
+    <t>Hà Nội, ngày 11 tháng 08 năm 2026</t>
   </si>
 </sst>
 </file>
@@ -116,7 +122,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0\ _₫_-;\-* #,##0\ _₫_-;_-* &quot;-&quot;\ _₫_-;_-@_-"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -147,12 +153,6 @@
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -167,25 +167,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <i/>
       <sz val="10"/>
       <color theme="1"/>
@@ -193,12 +174,6 @@
       <family val="1"/>
     </font>
     <font>
-      <i/>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="1"/>
@@ -220,6 +195,56 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -394,7 +419,7 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
@@ -404,158 +429,158 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="8"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="7"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="9"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="6"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="7"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="8"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="9"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="7"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="8"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -584,13 +609,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>488016</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>307038</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:colOff>307039</xdr:colOff>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -635,15 +660,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
+      <xdr:colOff>183931</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>95251</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>937846</xdr:colOff>
+      <xdr:colOff>931277</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>59375</xdr:rowOff>
+      <xdr:rowOff>79082</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -666,8 +691,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="190500" y="95251"/>
-          <a:ext cx="2242038" cy="469682"/>
+          <a:off x="183931" y="95251"/>
+          <a:ext cx="2245070" cy="476503"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -969,327 +994,296 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
     <col min="2" max="6" width="15.7109375" style="1" customWidth="1"/>
-    <col min="7" max="8" width="20.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" style="1" customWidth="1"/>
     <col min="9" max="14" width="9.140625" style="1" hidden="1" customWidth="1"/>
     <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="48" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="50"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="42"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="51" t="s">
+      <c r="A2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="52"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="42"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="51" t="s">
+      <c r="A3" s="16"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="52"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="28"/>
     </row>
     <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="45"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="53" t="s">
+      <c r="A4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="54"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="30"/>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="38"/>
-    </row>
-    <row r="6" spans="1:8" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="26"/>
+    </row>
+    <row r="6" spans="1:8" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="17" t="s">
+      <c r="B6" s="22"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="34" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="22" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="B7" s="22"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="1:8" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.2">
+      <c r="A8" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="36" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.2">
+      <c r="A9" s="53">
+        <v>1</v>
+      </c>
+      <c r="B9" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="17"/>
-    </row>
-    <row r="8" spans="1:8" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="26" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="25"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
+      <c r="D9" s="54">
+        <v>23</v>
+      </c>
+      <c r="E9" s="53"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="53"/>
     </row>
     <row r="10" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="10">
-        <v>1</v>
-      </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
     </row>
     <row r="11" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="10">
-        <v>2</v>
-      </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="11"/>
+      <c r="A11" s="39"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
       <c r="E11" s="10"/>
-      <c r="F11" s="12"/>
+      <c r="F11" s="10"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
     </row>
     <row r="12" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="10">
+      <c r="A12" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="39"/>
+      <c r="C12" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="39"/>
+      <c r="G12" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="H12" s="39"/>
+    </row>
+    <row r="13" spans="1:8" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-    </row>
-    <row r="13" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="50"/>
+      <c r="E13" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="48"/>
+      <c r="G13" s="52" t="s">
+        <v>3</v>
+      </c>
+      <c r="H13" s="48"/>
     </row>
     <row r="14" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+      <c r="A14" s="39"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="39"/>
     </row>
     <row r="15" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="16"/>
-      <c r="G15" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="H15" s="16"/>
-    </row>
-    <row r="16" spans="1:8" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="31"/>
-      <c r="E16" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="F16" s="29"/>
-      <c r="G16" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="H16" s="29"/>
+      <c r="A15" s="39"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="39"/>
+    </row>
+    <row r="16" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="39"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="39"/>
     </row>
     <row r="17" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="16"/>
+      <c r="A17" s="39"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
     </row>
     <row r="18" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="16"/>
-    </row>
-    <row r="19" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="16"/>
-    </row>
-    <row r="20" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-    </row>
+      <c r="A18" s="39"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="39"/>
+    </row>
+    <row r="19" spans="1:8" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="39"/>
+      <c r="C19" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="10"/>
+      <c r="E19" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" s="39"/>
+      <c r="G19" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="39"/>
+    </row>
+    <row r="20" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="21" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="16"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="16"/>
-    </row>
-    <row r="22" spans="1:8" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="H22" s="16"/>
-    </row>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+    </row>
+    <row r="22" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-    </row>
-    <row r="25" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:8" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+    </row>
     <row r="26" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:8" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-    </row>
-    <row r="29" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="35" spans="8:8" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="H35" s="5"/>
+    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="H32" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1300,8 +1294,8 @@
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="D4:H4"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="2" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageMargins left="1.2" right="1.2" top="1.5" bottom="1.5" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="94" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 08/XKSX_VoHopTG102LE(UPG)_170826.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 08/XKSX_VoHopTG102LE(UPG)_170826.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Xuất kho\Tháng 08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD18533-428B-4C7A-8E4E-2B69FF4A42BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6693CA-9F59-436F-A20D-984319104D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -122,7 +122,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0\ _₫_-;\-* #,##0\ _₫_-;_-* &quot;-&quot;\ _₫_-;_-@_-"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -239,11 +239,6 @@
     </font>
     <font>
       <i/>
-      <sz val="8"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -423,7 +418,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -457,39 +452,42 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="5"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -499,16 +497,31 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -520,68 +533,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="8"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="7"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="9"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="7"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="8"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -660,15 +628,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>183931</xdr:colOff>
+      <xdr:colOff>164224</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>95251</xdr:rowOff>
+      <xdr:rowOff>101820</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>931277</xdr:colOff>
+      <xdr:colOff>734208</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>79082</xdr:rowOff>
+      <xdr:rowOff>85651</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -691,7 +659,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="183931" y="95251"/>
+          <a:off x="164224" y="101820"/>
           <a:ext cx="2245070" cy="476503"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -998,95 +966,96 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
-    <col min="2" max="6" width="15.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="1" customWidth="1"/>
+    <col min="3" max="6" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" style="1" customWidth="1"/>
     <col min="9" max="14" width="9.140625" style="1" hidden="1" customWidth="1"/>
     <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="31" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="33"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="16"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="27" t="s">
+      <c r="A2" s="31"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="28"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="41"/>
     </row>
     <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="16"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="27" t="s">
+      <c r="A3" s="31"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="28"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="41"/>
     </row>
     <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="19"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="29" t="s">
+      <c r="A4" s="34"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="30"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="43"/>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="26"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="27"/>
     </row>
     <row r="6" spans="1:8" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="23"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="14"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="34" t="s">
+      <c r="H6" s="15" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="23"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="14"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="8"/>
@@ -1094,64 +1063,64 @@
       <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:8" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.2">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="36" t="s">
+      <c r="F8" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="36" t="s">
+      <c r="G8" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="36" t="s">
+      <c r="H8" s="17" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.2">
-      <c r="A9" s="53">
+      <c r="A9" s="23">
         <v>1</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="54">
-        <v>23</v>
-      </c>
-      <c r="E9" s="53"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="53" t="s">
+      <c r="D9" s="24">
+        <v>36</v>
+      </c>
+      <c r="E9" s="23"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="53"/>
+      <c r="H9" s="23"/>
     </row>
     <row r="10" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="37"/>
-      <c r="B10" s="37"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="10"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
     </row>
     <row r="11" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="39"/>
-      <c r="B11" s="39"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
@@ -1160,108 +1129,108 @@
       <c r="H11" s="10"/>
     </row>
     <row r="12" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="41" t="s">
+      <c r="B12" s="20"/>
+      <c r="C12" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="42" t="s">
+      <c r="D12" s="45"/>
+      <c r="E12" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="39"/>
-      <c r="G12" s="43" t="s">
+      <c r="F12" s="45"/>
+      <c r="G12" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="H12" s="39"/>
+      <c r="H12" s="45"/>
     </row>
     <row r="13" spans="1:8" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="47" t="s">
+      <c r="A13" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="48"/>
-      <c r="C13" s="49" t="s">
+      <c r="B13" s="44"/>
+      <c r="C13" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="50"/>
-      <c r="E13" s="51" t="s">
+      <c r="D13" s="44"/>
+      <c r="E13" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="F13" s="48"/>
-      <c r="G13" s="52" t="s">
+      <c r="F13" s="44"/>
+      <c r="G13" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="H13" s="48"/>
+      <c r="H13" s="44"/>
     </row>
     <row r="14" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="39"/>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="39"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="20"/>
     </row>
     <row r="15" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="39"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="39"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="20"/>
     </row>
     <row r="16" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="39"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="39"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="39"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="20"/>
     </row>
     <row r="17" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="39"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
     </row>
     <row r="18" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="39"/>
-      <c r="B18" s="39"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="39"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="20"/>
     </row>
     <row r="19" spans="1:8" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="39"/>
-      <c r="C19" s="42" t="s">
+      <c r="B19" s="45"/>
+      <c r="C19" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="46" t="s">
+      <c r="D19" s="45"/>
+      <c r="E19" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="F19" s="39"/>
-      <c r="G19" s="42" t="s">
+      <c r="F19" s="45"/>
+      <c r="G19" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="H19" s="39"/>
+      <c r="H19" s="45"/>
     </row>
     <row r="20" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="21" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -1286,7 +1255,18 @@
       <c r="H32" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="17">
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:H1"/>
@@ -1295,7 +1275,7 @@
     <mergeCell ref="D4:H4"/>
   </mergeCells>
   <pageMargins left="1.2" right="1.2" top="1.5" bottom="1.5" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="94" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="97" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>